--- a/Online Assessment 0/web_resources/Data files for Assessments/Online Assessment 0/Data3_8.xlsx
+++ b/Online Assessment 0/web_resources/Data files for Assessments/Online Assessment 0/Data3_8.xlsx
@@ -362,12 +362,12 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Group</t>
+          <t>Treatment?</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>InformationLevel</t>
+          <t>ReactionTime</t>
         </is>
       </c>
     </row>
@@ -378,10 +378,10 @@
         </is>
       </c>
       <c r="B2">
-        <v>-1.138714553960299</v>
+        <v>-0.9683967944885713</v>
       </c>
       <c r="C2">
-        <v>0.3797496724235795</v>
+        <v>0.3407191308067579</v>
       </c>
     </row>
     <row r="3">
@@ -391,10 +391,10 @@
         </is>
       </c>
       <c r="B3">
-        <v>-0.4517902097289269</v>
+        <v>-0.08260310018797161</v>
       </c>
       <c r="C3">
-        <v>0.3833110270673327</v>
+        <v>-0.7487225141276013</v>
       </c>
     </row>
     <row r="4">
@@ -404,10 +404,10 @@
         </is>
       </c>
       <c r="B4">
-        <v>-0.1404419728768061</v>
+        <v>-0.6596140815078034</v>
       </c>
       <c r="C4">
-        <v>0.837997527804498</v>
+        <v>1.570872219878138</v>
       </c>
     </row>
     <row r="5">
@@ -417,10 +417,10 @@
         </is>
       </c>
       <c r="B5">
-        <v>-0.01219423907399305</v>
+        <v>1.040165783654893</v>
       </c>
       <c r="C5">
-        <v>0.02507013251630543</v>
+        <v>1.079539301049643</v>
       </c>
     </row>
     <row r="6">
@@ -430,10 +430,10 @@
         </is>
       </c>
       <c r="B6">
-        <v>-0.6958846525707417</v>
+        <v>0.5920991640496671</v>
       </c>
       <c r="C6">
-        <v>-1.350097232939219</v>
+        <v>0.101951365490085</v>
       </c>
     </row>
     <row r="7">
@@ -443,10 +443,10 @@
         </is>
       </c>
       <c r="B7">
-        <v>-1.880091506832323</v>
+        <v>-0.1777787713931567</v>
       </c>
       <c r="C7">
-        <v>0.461353989654579</v>
+        <v>-0.1583909281929669</v>
       </c>
     </row>
     <row r="8">
@@ -456,10 +456,10 @@
         </is>
       </c>
       <c r="B8">
-        <v>-0.3114637597874765</v>
+        <v>0.7555399534386548</v>
       </c>
       <c r="C8">
-        <v>1.199971280853456</v>
+        <v>0.5975172341795454</v>
       </c>
     </row>
     <row r="9">
@@ -469,10 +469,10 @@
         </is>
       </c>
       <c r="B9">
-        <v>0.6558863353002297</v>
+        <v>-0.7742278887514015</v>
       </c>
       <c r="C9">
-        <v>0.391135447035626</v>
+        <v>-1.341760716402887</v>
       </c>
     </row>
     <row r="10">
@@ -482,10 +482,10 @@
         </is>
       </c>
       <c r="B10">
-        <v>0.2064827128022715</v>
+        <v>0.3114980299082784</v>
       </c>
       <c r="C10">
-        <v>-1.124944742986779</v>
+        <v>-0.4267201511363794</v>
       </c>
     </row>
     <row r="11">
@@ -495,10 +495,10 @@
         </is>
       </c>
       <c r="B11">
-        <v>0.3395216397675006</v>
+        <v>-0.6844578006325606</v>
       </c>
       <c r="C11">
-        <v>-2.90123599383462</v>
+        <v>-0.5946338721436073</v>
       </c>
     </row>
     <row r="12">
@@ -508,10 +508,10 @@
         </is>
       </c>
       <c r="B12">
-        <v>3.159810340339576</v>
+        <v>0.6873131556791743</v>
       </c>
       <c r="C12">
-        <v>0.4164944566334806</v>
+        <v>0.4364471420735535</v>
       </c>
     </row>
     <row r="13">
@@ -521,10 +521,10 @@
         </is>
       </c>
       <c r="B13">
-        <v>0.1091986836792615</v>
+        <v>-1.954604658444646</v>
       </c>
       <c r="C13">
-        <v>-0.09668111299805618</v>
+        <v>-0.944923790626029</v>
       </c>
     </row>
     <row r="14">
@@ -534,10 +534,10 @@
         </is>
       </c>
       <c r="B14">
-        <v>-0.575886267076303</v>
+        <v>-0.5500939958849947</v>
       </c>
       <c r="C14">
-        <v>1.471204121871395</v>
+        <v>-0.8579126233013513</v>
       </c>
     </row>
     <row r="15">
@@ -547,10 +547,10 @@
         </is>
       </c>
       <c r="B15">
-        <v>-0.3679054717275185</v>
+        <v>1.341878330703737</v>
       </c>
       <c r="C15">
-        <v>-0.6506887228773117</v>
+        <v>1.571371352736564</v>
       </c>
     </row>
     <row r="16">
@@ -560,10 +560,10 @@
         </is>
       </c>
       <c r="B16">
-        <v>-1.453633237328142</v>
+        <v>-1.18066277852084</v>
       </c>
       <c r="C16">
-        <v>0.4321924640522654</v>
+        <v>-1.359209118589165</v>
       </c>
     </row>
     <row r="17">
@@ -573,10 +573,10 @@
         </is>
       </c>
       <c r="B17">
-        <v>-0.8531227086361808</v>
+        <v>-0.6353681516356505</v>
       </c>
       <c r="C17">
-        <v>-0.84462471229978</v>
+        <v>-0.9012274358749293</v>
       </c>
     </row>
     <row r="18">
@@ -586,10 +586,10 @@
         </is>
       </c>
       <c r="B18">
-        <v>0.566266273485687</v>
+        <v>0.1692832722204786</v>
       </c>
       <c r="C18">
-        <v>0.2957893738111412</v>
+        <v>0.1408015336275</v>
       </c>
     </row>
     <row r="19">
@@ -599,10 +599,10 @@
         </is>
       </c>
       <c r="B19">
-        <v>-0.8248183966233178</v>
+        <v>1.196913428656884</v>
       </c>
       <c r="C19">
-        <v>-0.09322774280742653</v>
+        <v>0.752918246413748</v>
       </c>
     </row>
     <row r="20">
@@ -612,10 +612,10 @@
         </is>
       </c>
       <c r="B20">
-        <v>-1.682452005460985</v>
+        <v>1.245489501736603</v>
       </c>
       <c r="C20">
-        <v>-0.01396584645669354</v>
+        <v>0.8935071674677191</v>
       </c>
     </row>
     <row r="21">
@@ -625,10 +625,10 @@
         </is>
       </c>
       <c r="B21">
-        <v>0.02718147983118912</v>
+        <v>-0.02149240741171554</v>
       </c>
       <c r="C21">
-        <v>-0.1244123945064827</v>
+        <v>1.540839599779005</v>
       </c>
     </row>
     <row r="22">
@@ -638,10 +638,10 @@
         </is>
       </c>
       <c r="B22">
-        <v>-0.8394462142068466</v>
+        <v>-1.009057757858558</v>
       </c>
       <c r="C22">
-        <v>-0.1665795360591015</v>
+        <v>-0.3106462282839854</v>
       </c>
     </row>
     <row r="23">
@@ -651,10 +651,10 @@
         </is>
       </c>
       <c r="B23">
-        <v>-0.2285133520877577</v>
+        <v>0.2659961247430586</v>
       </c>
       <c r="C23">
-        <v>-1.604035369650931</v>
+        <v>1.871616818077275</v>
       </c>
     </row>
     <row r="24">
@@ -664,10 +664,10 @@
         </is>
       </c>
       <c r="B24">
-        <v>0.8416576221261949</v>
+        <v>-0.9859389533440059</v>
       </c>
       <c r="C24">
-        <v>0.2331916085689563</v>
+        <v>-0.3640140851041591</v>
       </c>
     </row>
     <row r="25">
@@ -677,10 +677,10 @@
         </is>
       </c>
       <c r="B25">
-        <v>-0.78449139818449</v>
+        <v>1.381920127211316</v>
       </c>
       <c r="C25">
-        <v>0.1999651798395749</v>
+        <v>1.49818926029027</v>
       </c>
     </row>
     <row r="26">
@@ -690,10 +690,10 @@
         </is>
       </c>
       <c r="B26">
-        <v>-0.04869924248254612</v>
+        <v>0.2495493452957825</v>
       </c>
       <c r="C26">
-        <v>0.2705744515922421</v>
+        <v>0.3387608879363605</v>
       </c>
     </row>
     <row r="27">
@@ -703,10 +703,10 @@
         </is>
       </c>
       <c r="B27">
-        <v>-1.11819147620973</v>
+        <v>-0.08170756619512604</v>
       </c>
       <c r="C27">
-        <v>0.7037788999029705</v>
+        <v>0.7145599126859296</v>
       </c>
     </row>
     <row r="28">
@@ -716,10 +716,10 @@
         </is>
       </c>
       <c r="B28">
-        <v>1.07775826009271</v>
+        <v>-0.4944670598673558</v>
       </c>
       <c r="C28">
-        <v>-0.3757369274070492</v>
+        <v>-0.7555990549819407</v>
       </c>
     </row>
     <row r="29">
@@ -729,10 +729,10 @@
         </is>
       </c>
       <c r="B29">
-        <v>-0.6390484294263477</v>
+        <v>0.1585547275532186</v>
       </c>
       <c r="C29">
-        <v>1.117125024320206</v>
+        <v>-0.6642717861701397</v>
       </c>
     </row>
     <row r="30">
@@ -742,10 +742,10 @@
         </is>
       </c>
       <c r="B30">
-        <v>0.1049437355679087</v>
+        <v>1.368496733042748</v>
       </c>
       <c r="C30">
-        <v>0.0265497124037391</v>
+        <v>0.5582016699409907</v>
       </c>
     </row>
     <row r="31">
@@ -755,10 +755,10 @@
         </is>
       </c>
       <c r="B31">
-        <v>0.1935226570070888</v>
+        <v>0.6957836307420213</v>
       </c>
       <c r="C31">
-        <v>1.108177009820285</v>
+        <v>-0.3890089139516847</v>
       </c>
     </row>
     <row r="32">
@@ -768,10 +768,10 @@
         </is>
       </c>
       <c r="B32">
-        <v>0.6949339399790619</v>
+        <v>-2.048527430133105</v>
       </c>
       <c r="C32">
-        <v>-2.118726752471783</v>
+        <v>-1.513179993973931</v>
       </c>
     </row>
     <row r="33">
@@ -781,10 +781,10 @@
         </is>
       </c>
       <c r="B33">
-        <v>-0.8675869978626032</v>
+        <v>1.065291847747373</v>
       </c>
       <c r="C33">
-        <v>-2.029673766165133</v>
+        <v>-0.3545619054932277</v>
       </c>
     </row>
     <row r="34">
@@ -794,10 +794,10 @@
         </is>
       </c>
       <c r="B34">
-        <v>0.6766651518382134</v>
+        <v>-0.001825989534918677</v>
       </c>
       <c r="C34">
-        <v>0.3786115501870516</v>
+        <v>-1.342078724801484</v>
       </c>
     </row>
     <row r="35">
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="B35">
-        <v>0.001335325629746951</v>
+        <v>-0.4669403862534343</v>
       </c>
       <c r="C35">
-        <v>0.4162343982274248</v>
+        <v>-0.7561414076997258</v>
       </c>
     </row>
     <row r="36">
@@ -820,10 +820,10 @@
         </is>
       </c>
       <c r="B36">
-        <v>-0.6555426265194646</v>
+        <v>1.343357573545221</v>
       </c>
       <c r="C36">
-        <v>0.9145546009776157</v>
+        <v>0.2369850082745958</v>
       </c>
     </row>
     <row r="37">
@@ -833,10 +833,10 @@
         </is>
       </c>
       <c r="B37">
-        <v>0.1172167429425071</v>
+        <v>0.8519086807706171</v>
       </c>
       <c r="C37">
-        <v>0.7679473023553152</v>
+        <v>0.2231623595618195</v>
       </c>
     </row>
     <row r="38">
@@ -846,10 +846,10 @@
         </is>
       </c>
       <c r="B38">
-        <v>-0.1262539026111888</v>
+        <v>-0.2559761730825668</v>
       </c>
       <c r="C38">
-        <v>-0.1891114413033763</v>
+        <v>0.7195421299402774</v>
       </c>
     </row>
     <row r="39">
@@ -859,10 +859,10 @@
         </is>
       </c>
       <c r="B39">
-        <v>0.1818141404388722</v>
+        <v>1.337202189894957</v>
       </c>
       <c r="C39">
-        <v>1.238185146481473</v>
+        <v>-0.4358277281765619</v>
       </c>
     </row>
     <row r="40">
@@ -872,10 +872,10 @@
         </is>
       </c>
       <c r="B40">
-        <v>-1.145718779624935</v>
+        <v>1.081557206345005</v>
       </c>
       <c r="C40">
-        <v>-1.041319812879289</v>
+        <v>1.245638010597636</v>
       </c>
     </row>
     <row r="41">
@@ -885,10 +885,10 @@
         </is>
       </c>
       <c r="B41">
-        <v>0.5392650969058436</v>
+        <v>0.682196357378055</v>
       </c>
       <c r="C41">
-        <v>-0.8533466609914333</v>
+        <v>-0.862183645027663</v>
       </c>
     </row>
     <row r="42">
@@ -898,10 +898,10 @@
         </is>
       </c>
       <c r="B42">
-        <v>0.5027530837685049</v>
+        <v>-1.204153939320077</v>
       </c>
       <c r="C42">
-        <v>-0.2683615770209573</v>
+        <v>-1.293750643824859</v>
       </c>
     </row>
     <row r="43">
@@ -911,10 +911,10 @@
         </is>
       </c>
       <c r="B43">
-        <v>1.307993109375976</v>
+        <v>-1.027309774462467</v>
       </c>
       <c r="C43">
-        <v>0.3631597816403501</v>
+        <v>0.9809781228495049</v>
       </c>
     </row>
     <row r="44">
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="B44">
-        <v>-0.9251800149234828</v>
+        <v>-0.09576105928327285</v>
       </c>
       <c r="C44">
-        <v>-3.001539693663672</v>
+        <v>1.26533826143525</v>
       </c>
     </row>
     <row r="45">
@@ -937,10 +937,10 @@
         </is>
       </c>
       <c r="B45">
-        <v>-0.1807167877690158</v>
+        <v>0.05659821379685349</v>
       </c>
       <c r="C45">
-        <v>1.229246931141497</v>
+        <v>-0.7877780517681486</v>
       </c>
     </row>
     <row r="46">
@@ -950,10 +950,10 @@
         </is>
       </c>
       <c r="B46">
-        <v>-0.8526029393155665</v>
+        <v>-1.652940545920119</v>
       </c>
       <c r="C46">
-        <v>1.326598377722701</v>
+        <v>-0.1369870341272181</v>
       </c>
     </row>
     <row r="47">
@@ -963,10 +963,10 @@
         </is>
       </c>
       <c r="B47">
-        <v>0.2235912020400741</v>
+        <v>1.332466424250134</v>
       </c>
       <c r="C47">
-        <v>0.4712229093329771</v>
+        <v>1.946136113942821</v>
       </c>
     </row>
     <row r="48">
@@ -976,10 +976,10 @@
         </is>
       </c>
       <c r="B48">
-        <v>-0.008587467597075167</v>
+        <v>-0.3268738460141193</v>
       </c>
       <c r="C48">
-        <v>-1.873205984612797</v>
+        <v>-0.2652704408885495</v>
       </c>
     </row>
     <row r="49">
@@ -989,10 +989,10 @@
         </is>
       </c>
       <c r="B49">
-        <v>0.4774868049372371</v>
+        <v>-0.6107504251203477</v>
       </c>
       <c r="C49">
-        <v>-1.155156077031132</v>
+        <v>2.946901704243818</v>
       </c>
     </row>
     <row r="50">
@@ -1002,10 +1002,10 @@
         </is>
       </c>
       <c r="B50">
-        <v>-0.2163385260101879</v>
+        <v>-0.8299929347434005</v>
       </c>
       <c r="C50">
-        <v>0.1598544594234275</v>
+        <v>-0.3407904901559983</v>
       </c>
     </row>
     <row r="51">
@@ -1015,10 +1015,10 @@
         </is>
       </c>
       <c r="B51">
-        <v>-0.4205908991451066</v>
+        <v>-0.7557059161454757</v>
       </c>
       <c r="C51">
-        <v>-0.09833955711471536</v>
+        <v>0.2323068057933984</v>
       </c>
     </row>
     <row r="52">
@@ -1028,10 +1028,10 @@
         </is>
       </c>
       <c r="B52">
-        <v>0.3037907701859962</v>
+        <v>-0.6062434886269676</v>
       </c>
       <c r="C52">
-        <v>0.8975536798434199</v>
+        <v>0.1484880562114042</v>
       </c>
     </row>
     <row r="53">
@@ -1041,10 +1041,10 @@
         </is>
       </c>
       <c r="B53">
-        <v>0.03108415504755204</v>
+        <v>2.005421013083903</v>
       </c>
       <c r="C53">
-        <v>0.15260336322152</v>
+        <v>2.362628474483776</v>
       </c>
     </row>
     <row r="54">
@@ -1054,10 +1054,10 @@
         </is>
       </c>
       <c r="B54">
-        <v>0.4014344444233856</v>
+        <v>0.8419712670586946</v>
       </c>
       <c r="C54">
-        <v>0.1130475239149561</v>
+        <v>-0.6896836736763603</v>
       </c>
     </row>
     <row r="55">
@@ -1067,10 +1067,10 @@
         </is>
       </c>
       <c r="B55">
-        <v>-1.061697087891838</v>
+        <v>0.7885012491992154</v>
       </c>
       <c r="C55">
-        <v>0.06676380167909558</v>
+        <v>1.23478630896085</v>
       </c>
     </row>
     <row r="56">
@@ -1080,10 +1080,10 @@
         </is>
       </c>
       <c r="B56">
-        <v>0.8857188559782915</v>
+        <v>-0.9421881706280324</v>
       </c>
       <c r="C56">
-        <v>2.076285364258835</v>
+        <v>-1.009284778301201</v>
       </c>
     </row>
     <row r="57">
@@ -1093,10 +1093,10 @@
         </is>
       </c>
       <c r="B57">
-        <v>-1.165382444886172</v>
+        <v>1.448551540834123</v>
       </c>
       <c r="C57">
-        <v>0.1930949278898877</v>
+        <v>0.2908791806720976</v>
       </c>
     </row>
     <row r="58">
@@ -1106,10 +1106,10 @@
         </is>
       </c>
       <c r="B58">
-        <v>-0.4939324121090162</v>
+        <v>0.617271138425123</v>
       </c>
       <c r="C58">
-        <v>0.6292813330752109</v>
+        <v>0.5334143710359882</v>
       </c>
     </row>
     <row r="59">
@@ -1119,10 +1119,10 @@
         </is>
       </c>
       <c r="B59">
-        <v>0.8225296313143747</v>
+        <v>-0.8068288711500762</v>
       </c>
       <c r="C59">
-        <v>-0.6034484565686377</v>
+        <v>0.427542678571213</v>
       </c>
     </row>
     <row r="60">
@@ -1132,10 +1132,10 @@
         </is>
       </c>
       <c r="B60">
-        <v>1.131722629530696</v>
+        <v>-0.6106117000820808</v>
       </c>
       <c r="C60">
-        <v>-0.8746054594201567</v>
+        <v>-1.263702482989518</v>
       </c>
     </row>
     <row r="61">
@@ -1145,10 +1145,10 @@
         </is>
       </c>
       <c r="B61">
-        <v>0.5250589795538001</v>
+        <v>0.3390444417040213</v>
       </c>
       <c r="C61">
-        <v>-0.5979208048356817</v>
+        <v>0.2301694491392636</v>
       </c>
     </row>
     <row r="62">
@@ -1158,10 +1158,10 @@
         </is>
       </c>
       <c r="B62">
-        <v>0.8644189940280136</v>
+        <v>-0.3211508044239049</v>
       </c>
       <c r="C62">
-        <v>0.2484860081594841</v>
+        <v>0.5019807767283209</v>
       </c>
     </row>
     <row r="63">
@@ -1171,10 +1171,10 @@
         </is>
       </c>
       <c r="B63">
-        <v>0.3918888535322017</v>
+        <v>1.528013302604102</v>
       </c>
       <c r="C63">
-        <v>-1.297475228938081</v>
+        <v>0.5265646271114999</v>
       </c>
     </row>
     <row r="64">
@@ -1184,10 +1184,10 @@
         </is>
       </c>
       <c r="B64">
-        <v>-0.01870903459070971</v>
+        <v>0.8375147485128553</v>
       </c>
       <c r="C64">
-        <v>-1.910135412228623</v>
+        <v>0.2968662703639858</v>
       </c>
     </row>
     <row r="65">
@@ -1197,10 +1197,10 @@
         </is>
       </c>
       <c r="B65">
-        <v>-0.7322347871809919</v>
+        <v>-0.1097268409877591</v>
       </c>
       <c r="C65">
-        <v>0.737224646000325</v>
+        <v>-0.306785147979849</v>
       </c>
     </row>
     <row r="66">
@@ -1210,10 +1210,10 @@
         </is>
       </c>
       <c r="B66">
-        <v>-2.734110339691214</v>
+        <v>-0.2841269511201455</v>
       </c>
       <c r="C66">
-        <v>-0.5079396463052926</v>
+        <v>-0.4188876394040896</v>
       </c>
     </row>
     <row r="67">
@@ -1223,10 +1223,10 @@
         </is>
       </c>
       <c r="B67">
-        <v>1.566528106805933</v>
+        <v>-1.06412905580279</v>
       </c>
       <c r="C67">
-        <v>0.1526224694514585</v>
+        <v>0.6918340983609579</v>
       </c>
     </row>
     <row r="68">
@@ -1236,10 +1236,10 @@
         </is>
       </c>
       <c r="B68">
-        <v>-1.115958546671318</v>
+        <v>0.6551837405042308</v>
       </c>
       <c r="C68">
-        <v>1.151751765049616</v>
+        <v>0.6708099259029845</v>
       </c>
     </row>
     <row r="69">
@@ -1249,10 +1249,10 @@
         </is>
       </c>
       <c r="B69">
-        <v>1.278091715073594</v>
+        <v>-1.832058037450769</v>
       </c>
       <c r="C69">
-        <v>0.9997779559030974</v>
+        <v>0.01336475992679043</v>
       </c>
     </row>
     <row r="70">
@@ -1262,10 +1262,10 @@
         </is>
       </c>
       <c r="B70">
-        <v>1.708052201672929</v>
+        <v>-0.819773474298693</v>
       </c>
       <c r="C70">
-        <v>2.158912525729141</v>
+        <v>-1.822852884681769</v>
       </c>
     </row>
     <row r="71">
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="B71">
-        <v>-1.861687166812934</v>
+        <v>-1.439808649442339</v>
       </c>
       <c r="C71">
-        <v>0.1299236101426157</v>
+        <v>-2.680005845151192</v>
       </c>
     </row>
     <row r="72">
@@ -1288,10 +1288,10 @@
         </is>
       </c>
       <c r="B72">
-        <v>0.5702336375331729</v>
+        <v>1.375004585551934</v>
       </c>
       <c r="C72">
-        <v>-0.001732681045109037</v>
+        <v>-0.5078350984348171</v>
       </c>
     </row>
     <row r="73">
@@ -1301,10 +1301,10 @@
         </is>
       </c>
       <c r="B73">
-        <v>-0.09128701054881451</v>
+        <v>-0.4717564910461608</v>
       </c>
       <c r="C73">
-        <v>-2.013359830546448</v>
+        <v>-1.526085605012986</v>
       </c>
     </row>
     <row r="74">
@@ -1314,10 +1314,10 @@
         </is>
       </c>
       <c r="B74">
-        <v>0.3863554317016789</v>
+        <v>1.211893267511604</v>
       </c>
       <c r="C74">
-        <v>0.6556415057122312</v>
+        <v>3.367659506439855</v>
       </c>
     </row>
     <row r="75">
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="B75">
-        <v>-0.6053641717020549</v>
+        <v>-0.391665955394498</v>
       </c>
       <c r="C75">
-        <v>0.9657398973810589</v>
+        <v>-1.014431872597846</v>
       </c>
     </row>
     <row r="76">
@@ -1340,10 +1340,10 @@
         </is>
       </c>
       <c r="B76">
-        <v>1.256214338902427</v>
+        <v>0.08251433671590445</v>
       </c>
       <c r="C76">
-        <v>-0.06413527056848141</v>
+        <v>-0.1824530124558011</v>
       </c>
     </row>
     <row r="77">
@@ -1353,10 +1353,10 @@
         </is>
       </c>
       <c r="B77">
-        <v>1.283455277839927</v>
+        <v>2.550304039981262</v>
       </c>
       <c r="C77">
-        <v>-2.239090691322431</v>
+        <v>-0.519071513477716</v>
       </c>
     </row>
     <row r="78">
@@ -1366,10 +1366,10 @@
         </is>
       </c>
       <c r="B78">
-        <v>1.401087107442301</v>
+        <v>0.156468265290716</v>
       </c>
       <c r="C78">
-        <v>0.7464282973465962</v>
+        <v>1.084944147622505</v>
       </c>
     </row>
     <row r="79">
@@ -1379,10 +1379,10 @@
         </is>
       </c>
       <c r="B79">
-        <v>0.5256137539568962</v>
+        <v>-0.8626203602689836</v>
       </c>
       <c r="C79">
-        <v>2.093938590611818</v>
+        <v>-0.7512300338829401</v>
       </c>
     </row>
     <row r="80">
@@ -1392,10 +1392,10 @@
         </is>
       </c>
       <c r="B80">
-        <v>0.9835623513349564</v>
+        <v>0.4237335406118286</v>
       </c>
       <c r="C80">
-        <v>1.245860712532205</v>
+        <v>-0.5120744343054627</v>
       </c>
     </row>
     <row r="81">
@@ -1405,10 +1405,10 @@
         </is>
       </c>
       <c r="B81">
-        <v>-1.809396776864244</v>
+        <v>0.5045262642832136</v>
       </c>
       <c r="C81">
-        <v>1.427839673370888</v>
+        <v>-0.6512694327575674</v>
       </c>
     </row>
     <row r="82">
@@ -1418,10 +1418,10 @@
         </is>
       </c>
       <c r="B82">
-        <v>1.230314216727664</v>
+        <v>1.106571187031711</v>
       </c>
       <c r="C82">
-        <v>0.6254963371664632</v>
+        <v>0.6829991188624948</v>
       </c>
     </row>
     <row r="83">
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="B83">
-        <v>-0.8806245434033702</v>
+        <v>-1.269615178455938</v>
       </c>
       <c r="C83">
-        <v>-1.031261933172648</v>
+        <v>-0.5787808230442368</v>
       </c>
     </row>
     <row r="84">
@@ -1444,10 +1444,10 @@
         </is>
       </c>
       <c r="B84">
-        <v>-0.1348899469337508</v>
+        <v>-0.4142674910826402</v>
       </c>
       <c r="C84">
-        <v>-1.129460440210669</v>
+        <v>0.9239582116538688</v>
       </c>
     </row>
     <row r="85">
@@ -1457,10 +1457,10 @@
         </is>
       </c>
       <c r="B85">
-        <v>-0.1891577862609954</v>
+        <v>-0.6838690386367099</v>
       </c>
       <c r="C85">
-        <v>0.6191592187662749</v>
+        <v>1.05996526553673</v>
       </c>
     </row>
     <row r="86">
@@ -1470,10 +1470,10 @@
         </is>
       </c>
       <c r="B86">
-        <v>-1.832853824628834</v>
+        <v>0.7922947851565242</v>
       </c>
       <c r="C86">
-        <v>-1.323608638221496</v>
+        <v>-0.5613057245049896</v>
       </c>
     </row>
     <row r="87">
@@ -1483,10 +1483,10 @@
         </is>
       </c>
       <c r="B87">
-        <v>0.5652153754851977</v>
+        <v>1.70177584132586</v>
       </c>
       <c r="C87">
-        <v>-0.8523431103715754</v>
+        <v>1.239806226455642</v>
       </c>
     </row>
     <row r="88">
@@ -1496,10 +1496,10 @@
         </is>
       </c>
       <c r="B88">
-        <v>0.3522112641414736</v>
+        <v>-0.2149733673508644</v>
       </c>
       <c r="C88">
-        <v>1.052568150753398</v>
+        <v>-1.158627736733278</v>
       </c>
     </row>
     <row r="89">
@@ -1509,10 +1509,10 @@
         </is>
       </c>
       <c r="B89">
-        <v>-1.170990359735316</v>
+        <v>-2.597676934863458</v>
       </c>
       <c r="C89">
-        <v>-1.38572714637911</v>
+        <v>-0.7650989339115601</v>
       </c>
     </row>
     <row r="90">
@@ -1522,10 +1522,10 @@
         </is>
       </c>
       <c r="B90">
-        <v>-0.9708003302746949</v>
+        <v>-1.070850969921306</v>
       </c>
       <c r="C90">
-        <v>0.1799254280508782</v>
+        <v>-0.9416967802580912</v>
       </c>
     </row>
     <row r="91">
@@ -1535,10 +1535,10 @@
         </is>
       </c>
       <c r="B91">
-        <v>0.2870681295148139</v>
+        <v>0.3542101776907227</v>
       </c>
       <c r="C91">
-        <v>0.06348888792253439</v>
+        <v>-0.9909459011549421</v>
       </c>
     </row>
     <row r="92">
@@ -1548,10 +1548,10 @@
         </is>
       </c>
       <c r="B92">
-        <v>-0.4244950630536257</v>
+        <v>1.633215636664493</v>
       </c>
       <c r="C92">
-        <v>1.521681336592448</v>
+        <v>0.8443920672290008</v>
       </c>
     </row>
     <row r="93">
@@ -1561,10 +1561,10 @@
         </is>
       </c>
       <c r="B93">
-        <v>-1.502044715055883</v>
+        <v>0.02589472604275082</v>
       </c>
       <c r="C93">
-        <v>-0.3257777498739898</v>
+        <v>0.3991527209812231</v>
       </c>
     </row>
     <row r="94">
@@ -1574,10 +1574,10 @@
         </is>
       </c>
       <c r="B94">
-        <v>-0.8662938625797264</v>
+        <v>-0.3720656368751231</v>
       </c>
       <c r="C94">
-        <v>1.459491318771735</v>
+        <v>-0.958316144890175</v>
       </c>
     </row>
     <row r="95">
@@ -1587,10 +1587,10 @@
         </is>
       </c>
       <c r="B95">
-        <v>-0.1109624267737446</v>
+        <v>0.3567911467422946</v>
       </c>
       <c r="C95">
-        <v>0.3643354068646276</v>
+        <v>0.531595217377357</v>
       </c>
     </row>
     <row r="96">
@@ -1600,10 +1600,10 @@
         </is>
       </c>
       <c r="B96">
-        <v>-0.2385360782193096</v>
+        <v>0.586307135353603</v>
       </c>
       <c r="C96">
-        <v>0.0159379990273841</v>
+        <v>0.1703810550201031</v>
       </c>
     </row>
     <row r="97">
@@ -1613,10 +1613,10 @@
         </is>
       </c>
       <c r="B97">
-        <v>-0.005934888060322174</v>
+        <v>0.2380543324279048</v>
       </c>
       <c r="C97">
-        <v>-0.8897230233042847</v>
+        <v>-0.4170901008514026</v>
       </c>
     </row>
     <row r="98">
@@ -1626,10 +1626,10 @@
         </is>
       </c>
       <c r="B98">
-        <v>0.4391512374853948</v>
+        <v>-0.8910330480401173</v>
       </c>
       <c r="C98">
-        <v>0.1949289306819229</v>
+        <v>-1.59757069897479</v>
       </c>
     </row>
     <row r="99">
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="B99">
-        <v>0.5886174818510621</v>
+        <v>0.05177557091713485</v>
       </c>
       <c r="C99">
-        <v>1.07874110208702</v>
+        <v>0.5548475786862516</v>
       </c>
     </row>
     <row r="100">
@@ -1652,10 +1652,10 @@
         </is>
       </c>
       <c r="B100">
-        <v>0.4743095149103219</v>
+        <v>-0.2385966762595611</v>
       </c>
       <c r="C100">
-        <v>-0.9684202256693619</v>
+        <v>-0.04760618531914194</v>
       </c>
     </row>
     <row r="101">
@@ -1665,10 +1665,10 @@
         </is>
       </c>
       <c r="B101">
-        <v>0.6444601923198557</v>
+        <v>0.3567608377080427</v>
       </c>
       <c r="C101">
-        <v>-0.8128728417822108</v>
+        <v>0.9022533445769126</v>
       </c>
     </row>
     <row r="102">
@@ -1678,10 +1678,10 @@
         </is>
       </c>
       <c r="B102">
-        <v>0.49569698203274</v>
+        <v>0.03747444928275215</v>
       </c>
       <c r="C102">
-        <v>0.3197102711314485</v>
+        <v>-0.6714586488047273</v>
       </c>
     </row>
     <row r="103">
@@ -1691,10 +1691,10 @@
         </is>
       </c>
       <c r="B103">
-        <v>-0.496190647421666</v>
+        <v>-0.6636005716895292</v>
       </c>
       <c r="C103">
-        <v>-1.415902124933721</v>
+        <v>-1.304361716714989</v>
       </c>
     </row>
     <row r="104">
@@ -1704,10 +1704,10 @@
         </is>
       </c>
       <c r="B104">
-        <v>0.1331861660847103</v>
+        <v>0.1077337285669852</v>
       </c>
       <c r="C104">
-        <v>-0.1614551828560301</v>
+        <v>0.7135577492452574</v>
       </c>
     </row>
     <row r="105">
@@ -1717,10 +1717,10 @@
         </is>
       </c>
       <c r="B105">
-        <v>-0.4147450010721171</v>
+        <v>1.393580048170502</v>
       </c>
       <c r="C105">
-        <v>-0.4185136955771901</v>
+        <v>0.3324811695608219</v>
       </c>
     </row>
     <row r="106">
@@ -1730,10 +1730,10 @@
         </is>
       </c>
       <c r="B106">
-        <v>1.259197740605333</v>
+        <v>0.3831529016280087</v>
       </c>
       <c r="C106">
-        <v>-0.5048234890592771</v>
+        <v>1.920598479200982</v>
       </c>
     </row>
     <row r="107">
@@ -1743,10 +1743,10 @@
         </is>
       </c>
       <c r="B107">
-        <v>-0.4073812737448049</v>
+        <v>0.1544039916813378</v>
       </c>
       <c r="C107">
-        <v>0.705457741342629</v>
+        <v>0.9502284615813202</v>
       </c>
     </row>
     <row r="108">
@@ -1756,10 +1756,10 @@
         </is>
       </c>
       <c r="B108">
-        <v>-2.261190511645915</v>
+        <v>-0.2454480059803195</v>
       </c>
       <c r="C108">
-        <v>0.6047226322145319</v>
+        <v>-0.05403500444970399</v>
       </c>
     </row>
     <row r="109">
@@ -1769,10 +1769,10 @@
         </is>
       </c>
       <c r="B109">
-        <v>0.7674247497610072</v>
+        <v>-0.2107578779064243</v>
       </c>
       <c r="C109">
-        <v>-0.2220075443033275</v>
+        <v>-0.06226585213398675</v>
       </c>
     </row>
     <row r="110">
@@ -1782,10 +1782,10 @@
         </is>
       </c>
       <c r="B110">
-        <v>-0.8570756638162531</v>
+        <v>-1.137819628805719</v>
       </c>
       <c r="C110">
-        <v>1.088233500650811</v>
+        <v>-3.015572978733775</v>
       </c>
     </row>
     <row r="111">
@@ -1795,10 +1795,10 @@
         </is>
       </c>
       <c r="B111">
-        <v>-0.9052038626111315</v>
+        <v>0.7326953944938962</v>
       </c>
       <c r="C111">
-        <v>-0.6701572421768475</v>
+        <v>0.3965698500894056</v>
       </c>
     </row>
     <row r="112">
@@ -1808,10 +1808,10 @@
         </is>
       </c>
       <c r="B112">
-        <v>-1.078860128614994</v>
+        <v>-1.509479767432913</v>
       </c>
       <c r="C112">
-        <v>-0.7306085572850157</v>
+        <v>-0.2349666336321534</v>
       </c>
     </row>
     <row r="113">
@@ -1821,10 +1821,10 @@
         </is>
       </c>
       <c r="B113">
-        <v>-0.2810215764167339</v>
+        <v>0.5456341746424533</v>
       </c>
       <c r="C113">
-        <v>1.241922580851624</v>
+        <v>-1.375114911470273</v>
       </c>
     </row>
     <row r="114">
@@ -1834,10 +1834,10 @@
         </is>
       </c>
       <c r="B114">
-        <v>0.7429514822732661</v>
+        <v>1.270856316436171</v>
       </c>
       <c r="C114">
-        <v>-0.2269194578075206</v>
+        <v>0.8123592365863226</v>
       </c>
     </row>
     <row r="115">
@@ -1847,10 +1847,10 @@
         </is>
       </c>
       <c r="B115">
-        <v>0.4271113073948712</v>
+        <v>-1.074491231154103</v>
       </c>
       <c r="C115">
-        <v>0.4270756467465675</v>
+        <v>-0.4306138743046349</v>
       </c>
     </row>
     <row r="116">
@@ -1860,10 +1860,10 @@
         </is>
       </c>
       <c r="B116">
-        <v>-1.423284097877953</v>
+        <v>-1.674884217771411</v>
       </c>
       <c r="C116">
-        <v>0.5161779095327714</v>
+        <v>1.015597650885598</v>
       </c>
     </row>
     <row r="117">
@@ -1873,10 +1873,10 @@
         </is>
       </c>
       <c r="B117">
-        <v>-1.822622259083397</v>
+        <v>2.298053390816367</v>
       </c>
       <c r="C117">
-        <v>1.969622266770175</v>
+        <v>1.754500884734419</v>
       </c>
     </row>
     <row r="118">
@@ -1886,10 +1886,10 @@
         </is>
       </c>
       <c r="B118">
-        <v>-0.6390050337655448</v>
+        <v>0.6813081347961488</v>
       </c>
       <c r="C118">
-        <v>0.2207032124352874</v>
+        <v>0.7785249161461427</v>
       </c>
     </row>
     <row r="119">
@@ -1899,10 +1899,10 @@
         </is>
       </c>
       <c r="B119">
-        <v>-0.5438327771351859</v>
+        <v>0.3134088565938867</v>
       </c>
       <c r="C119">
-        <v>0.3731066778461083</v>
+        <v>0.547460357766512</v>
       </c>
     </row>
     <row r="120">
@@ -1912,10 +1912,10 @@
         </is>
       </c>
       <c r="B120">
-        <v>0.5974477194242787</v>
+        <v>-1.040612079304315</v>
       </c>
       <c r="C120">
-        <v>-1.015462799357507</v>
+        <v>-0.3604328771584161</v>
       </c>
     </row>
     <row r="121">
@@ -1925,10 +1925,10 @@
         </is>
       </c>
       <c r="B121">
-        <v>-0.8606236128056269</v>
+        <v>-0.8291048636898063</v>
       </c>
       <c r="C121">
-        <v>1.369274372675632</v>
+        <v>-0.6610466217295669</v>
       </c>
     </row>
     <row r="122">
@@ -1938,10 +1938,10 @@
         </is>
       </c>
       <c r="B122">
-        <v>-0.07086916761640011</v>
+        <v>1.32127612740552</v>
       </c>
       <c r="C122">
-        <v>-0.6913594513457062</v>
+        <v>1.070525271202494</v>
       </c>
     </row>
     <row r="123">
@@ -1951,10 +1951,10 @@
         </is>
       </c>
       <c r="B123">
-        <v>0.2848635799091281</v>
+        <v>0.1012433712033324</v>
       </c>
       <c r="C123">
-        <v>-0.6656589189885584</v>
+        <v>-0.8260293074877827</v>
       </c>
     </row>
     <row r="124">
@@ -1964,10 +1964,10 @@
         </is>
       </c>
       <c r="B124">
-        <v>-0.06037694382905601</v>
+        <v>0.2626678432315557</v>
       </c>
       <c r="C124">
-        <v>-0.02710867622357954</v>
+        <v>-2.035692296911151</v>
       </c>
     </row>
     <row r="125">
@@ -1977,10 +1977,10 @@
         </is>
       </c>
       <c r="B125">
-        <v>0.04181018620806658</v>
+        <v>-1.114842117412423</v>
       </c>
       <c r="C125">
-        <v>-0.1668119790949944</v>
+        <v>-2.822936221057744</v>
       </c>
     </row>
     <row r="126">
@@ -1990,10 +1990,10 @@
         </is>
       </c>
       <c r="B126">
-        <v>-0.2363614054490228</v>
+        <v>-0.7157996366450319</v>
       </c>
       <c r="C126">
-        <v>1.249305639786769</v>
+        <v>1.334386349132499</v>
       </c>
     </row>
     <row r="127">
@@ -2003,10 +2003,10 @@
         </is>
       </c>
       <c r="B127">
-        <v>0.8960622161231497</v>
+        <v>0.3223506960473961</v>
       </c>
       <c r="C127">
-        <v>0.09896272941957933</v>
+        <v>-1.373081771080297</v>
       </c>
     </row>
     <row r="128">
@@ -2016,10 +2016,10 @@
         </is>
       </c>
       <c r="B128">
-        <v>0.4898733215626427</v>
+        <v>1.048323890071273</v>
       </c>
       <c r="C128">
-        <v>-0.8366436006774308</v>
+        <v>-0.4650989357070417</v>
       </c>
     </row>
     <row r="129">
@@ -2029,10 +2029,10 @@
         </is>
       </c>
       <c r="B129">
-        <v>-1.111728103460913</v>
+        <v>0.0917715174069815</v>
       </c>
       <c r="C129">
-        <v>1.147447110538806</v>
+        <v>2.65936173769307</v>
       </c>
     </row>
     <row r="130">
@@ -2042,10 +2042,10 @@
         </is>
       </c>
       <c r="B130">
-        <v>-0.9627454180484831</v>
+        <v>0.5368307278886558</v>
       </c>
       <c r="C130">
-        <v>-0.02479034533483531</v>
+        <v>0.3234684515041941</v>
       </c>
     </row>
     <row r="131">
@@ -2055,10 +2055,10 @@
         </is>
       </c>
       <c r="B131">
-        <v>1.0079126373597</v>
+        <v>0.4027429648979969</v>
       </c>
       <c r="C131">
-        <v>-0.6024461468997637</v>
+        <v>1.818491835364055</v>
       </c>
     </row>
     <row r="132">
@@ -2068,10 +2068,10 @@
         </is>
       </c>
       <c r="B132">
-        <v>2.087307051420938</v>
+        <v>-0.9075028551191846</v>
       </c>
       <c r="C132">
-        <v>0.7338186279526758</v>
+        <v>-0.2598355975841526</v>
       </c>
     </row>
     <row r="133">
@@ -2081,10 +2081,10 @@
         </is>
       </c>
       <c r="B133">
-        <v>-0.475117128426456</v>
+        <v>-0.4720690965948867</v>
       </c>
       <c r="C133">
-        <v>-1.36279394658605</v>
+        <v>-1.696918359581439</v>
       </c>
     </row>
     <row r="134">
@@ -2094,10 +2094,10 @@
         </is>
       </c>
       <c r="B134">
-        <v>0.3546043012289045</v>
+        <v>-0.4396717654744062</v>
       </c>
       <c r="C134">
-        <v>-0.4549525612442072</v>
+        <v>0.3971751082844854</v>
       </c>
     </row>
     <row r="135">
@@ -2107,10 +2107,10 @@
         </is>
       </c>
       <c r="B135">
-        <v>1.899203719719932</v>
+        <v>-1.07800272184805</v>
       </c>
       <c r="C135">
-        <v>0.3404861009837743</v>
+        <v>-1.218786193452946</v>
       </c>
     </row>
     <row r="136">
@@ -2120,10 +2120,10 @@
         </is>
       </c>
       <c r="B136">
-        <v>0.5291961224627367</v>
+        <v>-1.622185583628688</v>
       </c>
       <c r="C136">
-        <v>0.8166496426049363</v>
+        <v>-0.9425228787760365</v>
       </c>
     </row>
     <row r="137">
@@ -2133,10 +2133,10 @@
         </is>
       </c>
       <c r="B137">
-        <v>1.939008942583196</v>
+        <v>-0.3856070254111255</v>
       </c>
       <c r="C137">
-        <v>-2.412509401256082</v>
+        <v>-0.2053356699750845</v>
       </c>
     </row>
     <row r="138">
@@ -2146,10 +2146,10 @@
         </is>
       </c>
       <c r="B138">
-        <v>-2.727417643866336</v>
+        <v>-0.9606202999317586</v>
       </c>
       <c r="C138">
-        <v>-1.732406242020755</v>
+        <v>-1.402588574249634</v>
       </c>
     </row>
     <row r="139">
@@ -2159,10 +2159,10 @@
         </is>
       </c>
       <c r="B139">
-        <v>-0.4790082420023935</v>
+        <v>0.5125350452524047</v>
       </c>
       <c r="C139">
-        <v>-0.3320979932253993</v>
+        <v>0.7316027694720504</v>
       </c>
     </row>
     <row r="140">
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="B140">
-        <v>0.7543481186335447</v>
+        <v>0.8865141929476564</v>
       </c>
       <c r="C140">
-        <v>0.679457934570551</v>
+        <v>0.5983289201497581</v>
       </c>
     </row>
     <row r="141">
@@ -2185,10 +2185,10 @@
         </is>
       </c>
       <c r="B141">
-        <v>1.221201266378626</v>
+        <v>-0.1980698047742226</v>
       </c>
       <c r="C141">
-        <v>1.102473789507391</v>
+        <v>-0.120704638965688</v>
       </c>
     </row>
     <row r="142">
@@ -2198,10 +2198,10 @@
         </is>
       </c>
       <c r="B142">
-        <v>1.5116009532509</v>
+        <v>0.6539396330378415</v>
       </c>
       <c r="C142">
-        <v>0.1286902008235061</v>
+        <v>1.579503758762803</v>
       </c>
     </row>
     <row r="143">
@@ -2211,10 +2211,10 @@
         </is>
       </c>
       <c r="B143">
-        <v>0.9805554083981711</v>
+        <v>0.177385895230384</v>
       </c>
       <c r="C143">
-        <v>0.4352273266274298</v>
+        <v>0.3894741918512473</v>
       </c>
     </row>
     <row r="144">
@@ -2224,10 +2224,10 @@
         </is>
       </c>
       <c r="B144">
-        <v>1.468180963684356</v>
+        <v>0.02417377051394275</v>
       </c>
       <c r="C144">
-        <v>1.183147010949708</v>
+        <v>1.454248532509053</v>
       </c>
     </row>
     <row r="145">
@@ -2237,10 +2237,10 @@
         </is>
       </c>
       <c r="B145">
-        <v>1.055492716071978</v>
+        <v>-0.5100901932856056</v>
       </c>
       <c r="C145">
-        <v>1.072011047090269</v>
+        <v>-0.7716043260072993</v>
       </c>
     </row>
     <row r="146">
@@ -2250,10 +2250,10 @@
         </is>
       </c>
       <c r="B146">
-        <v>-0.871259070898352</v>
+        <v>0.3881801376839786</v>
       </c>
       <c r="C146">
-        <v>-1.552997403071925</v>
+        <v>1.210402573409038</v>
       </c>
     </row>
     <row r="147">
@@ -2263,10 +2263,10 @@
         </is>
       </c>
       <c r="B147">
-        <v>0.1523296700671276</v>
+        <v>0.1473031038355167</v>
       </c>
       <c r="C147">
-        <v>0.7704449565545904</v>
+        <v>1.175183229095606</v>
       </c>
     </row>
     <row r="148">
@@ -2276,10 +2276,10 @@
         </is>
       </c>
       <c r="B148">
-        <v>0.5098500055825416</v>
+        <v>-0.7316422286198786</v>
       </c>
       <c r="C148">
-        <v>1.918352367253953</v>
+        <v>-0.2811797995730873</v>
       </c>
     </row>
     <row r="149">
@@ -2289,10 +2289,10 @@
         </is>
       </c>
       <c r="B149">
-        <v>-0.8167651683283705</v>
+        <v>1.319172943519192</v>
       </c>
       <c r="C149">
-        <v>-0.8057105283454395</v>
+        <v>0.6126013833206987</v>
       </c>
     </row>
     <row r="150">
@@ -2302,10 +2302,10 @@
         </is>
       </c>
       <c r="B150">
-        <v>1.534176796254373</v>
+        <v>-0.1738620584438494</v>
       </c>
       <c r="C150">
-        <v>0.125968260539939</v>
+        <v>0.5558400009740795</v>
       </c>
     </row>
     <row r="151">
@@ -2315,10 +2315,10 @@
         </is>
       </c>
       <c r="B151">
-        <v>1.707084680428155</v>
+        <v>-1.150169035770393</v>
       </c>
       <c r="C151">
-        <v>-0.2581565783817391</v>
+        <v>-1.097147185967174</v>
       </c>
     </row>
     <row r="152">
@@ -2328,10 +2328,10 @@
         </is>
       </c>
       <c r="B152">
-        <v>-2.061640267345263</v>
+        <v>0.2544138795731042</v>
       </c>
       <c r="C152">
-        <v>-0.6271919410688372</v>
+        <v>-0.66427143446838</v>
       </c>
     </row>
     <row r="153">
@@ -2341,10 +2341,10 @@
         </is>
       </c>
       <c r="B153">
-        <v>-1.659218492132822</v>
+        <v>-0.9598354154480053</v>
       </c>
       <c r="C153">
-        <v>-1.205693908084552</v>
+        <v>-1.366981607441365</v>
       </c>
     </row>
     <row r="154">
@@ -2354,10 +2354,10 @@
         </is>
       </c>
       <c r="B154">
-        <v>1.713040112049907</v>
+        <v>0.6918733096817101</v>
       </c>
       <c r="C154">
-        <v>-0.01154053065234467</v>
+        <v>-0.6040364065315074</v>
       </c>
     </row>
     <row r="155">
@@ -2367,10 +2367,10 @@
         </is>
       </c>
       <c r="B155">
-        <v>-1.440859486121257</v>
+        <v>-0.5665290710710391</v>
       </c>
       <c r="C155">
-        <v>-0.2756565255870879</v>
+        <v>0.2197639796275692</v>
       </c>
     </row>
     <row r="156">
@@ -2380,10 +2380,10 @@
         </is>
       </c>
       <c r="B156">
-        <v>1.101335837434667</v>
+        <v>0.587951117726032</v>
       </c>
       <c r="C156">
-        <v>1.520465317416649</v>
+        <v>-0.3741332417854208</v>
       </c>
     </row>
     <row r="157">
@@ -2393,10 +2393,10 @@
         </is>
       </c>
       <c r="B157">
-        <v>0.5762146515252015</v>
+        <v>-1.0413664297971</v>
       </c>
       <c r="C157">
-        <v>-1.076081216696893</v>
+        <v>-0.6087649502341019</v>
       </c>
     </row>
     <row r="158">
@@ -2406,10 +2406,10 @@
         </is>
       </c>
       <c r="B158">
-        <v>-0.4016559826873704</v>
+        <v>2.604465654570899</v>
       </c>
       <c r="C158">
-        <v>-0.8732552748722244</v>
+        <v>0.3907000213966432</v>
       </c>
     </row>
     <row r="159">
@@ -2419,10 +2419,10 @@
         </is>
       </c>
       <c r="B159">
-        <v>1.22050492367087</v>
+        <v>-0.241586575601106</v>
       </c>
       <c r="C159">
-        <v>0.3233383151368831</v>
+        <v>0.1732584344337701</v>
       </c>
     </row>
     <row r="160">
@@ -2432,10 +2432,10 @@
         </is>
       </c>
       <c r="B160">
-        <v>-0.5884914310850038</v>
+        <v>0.5745370488144863</v>
       </c>
       <c r="C160">
-        <v>1.124511984782755</v>
+        <v>0.07904780535741929</v>
       </c>
     </row>
     <row r="161">
@@ -2445,10 +2445,10 @@
         </is>
       </c>
       <c r="B161">
-        <v>-0.4696227132418784</v>
+        <v>1.316312729679547</v>
       </c>
       <c r="C161">
-        <v>1.816329280563049</v>
+        <v>0.143532302821809</v>
       </c>
     </row>
     <row r="162">
@@ -2458,10 +2458,10 @@
         </is>
       </c>
       <c r="B162">
-        <v>0.3473438564443925</v>
+        <v>-0.3390346715988836</v>
       </c>
       <c r="C162">
-        <v>1.074278968504144</v>
+        <v>0.2132740539207829</v>
       </c>
     </row>
     <row r="163">
@@ -2471,10 +2471,10 @@
         </is>
       </c>
       <c r="B163">
-        <v>-0.9974600968239893</v>
+        <v>0.1727567436235218</v>
       </c>
       <c r="C163">
-        <v>0.1534444688049905</v>
+        <v>-0.2447674643457548</v>
       </c>
     </row>
     <row r="164">
@@ -2484,10 +2484,10 @@
         </is>
       </c>
       <c r="B164">
-        <v>-0.1780025030551554</v>
+        <v>-1.745286873479406</v>
       </c>
       <c r="C164">
-        <v>0.4254299483128459</v>
+        <v>-1.27634952444145</v>
       </c>
     </row>
     <row r="165">
@@ -2497,10 +2497,10 @@
         </is>
       </c>
       <c r="B165">
-        <v>-0.7401014420806357</v>
+        <v>-1.319474677775186</v>
       </c>
       <c r="C165">
-        <v>-1.216844743625705</v>
+        <v>0.8529592765673133</v>
       </c>
     </row>
     <row r="166">
@@ -2510,10 +2510,10 @@
         </is>
       </c>
       <c r="B166">
-        <v>0.5566154781078609</v>
+        <v>-1.379808076638073</v>
       </c>
       <c r="C166">
-        <v>0.7090784581726567</v>
+        <v>-1.630378885021811</v>
       </c>
     </row>
     <row r="167">
@@ -2523,10 +2523,10 @@
         </is>
       </c>
       <c r="B167">
-        <v>0.887846794559757</v>
+        <v>-0.05727394136407185</v>
       </c>
       <c r="C167">
-        <v>-1.469562436802562</v>
+        <v>-0.2689899158524514</v>
       </c>
     </row>
     <row r="168">
@@ -2536,10 +2536,10 @@
         </is>
       </c>
       <c r="B168">
-        <v>-0.3579788607271766</v>
+        <v>1.017021645147679</v>
       </c>
       <c r="C168">
-        <v>-0.4127202869416998</v>
+        <v>0.1258278117028091</v>
       </c>
     </row>
     <row r="169">
@@ -2549,10 +2549,10 @@
         </is>
       </c>
       <c r="B169">
-        <v>-2.187915900151897</v>
+        <v>1.857692196167359</v>
       </c>
       <c r="C169">
-        <v>0.4663963970756038</v>
+        <v>1.49542792641494</v>
       </c>
     </row>
     <row r="170">
@@ -2562,10 +2562,10 @@
         </is>
       </c>
       <c r="B170">
-        <v>-0.1613267304941352</v>
+        <v>-1.368011772376648</v>
       </c>
       <c r="C170">
-        <v>0.6994449732047524</v>
+        <v>-2.254702558473613</v>
       </c>
     </row>
     <row r="171">
@@ -2575,10 +2575,10 @@
         </is>
       </c>
       <c r="B171">
-        <v>-0.1186626367066745</v>
+        <v>-1.786781501912988</v>
       </c>
       <c r="C171">
-        <v>-1.061464472019035</v>
+        <v>-0.9005920130594487</v>
       </c>
     </row>
     <row r="172">
@@ -2588,10 +2588,10 @@
         </is>
       </c>
       <c r="B172">
-        <v>0.3708561678924223</v>
+        <v>0.7385104729788984</v>
       </c>
       <c r="C172">
-        <v>0.2366972986463205</v>
+        <v>0.8291651328229275</v>
       </c>
     </row>
     <row r="173">
@@ -2601,10 +2601,10 @@
         </is>
       </c>
       <c r="B173">
-        <v>0.380506035648822</v>
+        <v>0.3173997548362934</v>
       </c>
       <c r="C173">
-        <v>-1.151917662770064</v>
+        <v>0.9127534144711023</v>
       </c>
     </row>
     <row r="174">
@@ -2614,10 +2614,10 @@
         </is>
       </c>
       <c r="B174">
-        <v>0.6112916498456303</v>
+        <v>-1.537225950754428</v>
       </c>
       <c r="C174">
-        <v>-1.014331616067027</v>
+        <v>0.379215884496077</v>
       </c>
     </row>
     <row r="175">
@@ -2627,10 +2627,10 @@
         </is>
       </c>
       <c r="B175">
-        <v>0.3296747316356374</v>
+        <v>0.1413916927919715</v>
       </c>
       <c r="C175">
-        <v>-0.883802437585568</v>
+        <v>-1.971936817913953</v>
       </c>
     </row>
     <row r="176">
@@ -2640,10 +2640,10 @@
         </is>
       </c>
       <c r="B176">
-        <v>-1.120933420704724</v>
+        <v>-0.7230848051044224</v>
       </c>
       <c r="C176">
-        <v>1.361675470265789</v>
+        <v>-0.1860511873966218</v>
       </c>
     </row>
     <row r="177">
@@ -2653,10 +2653,10 @@
         </is>
       </c>
       <c r="B177">
-        <v>-1.077797571353442</v>
+        <v>0.5636411245708548</v>
       </c>
       <c r="C177">
-        <v>0.2045796104774038</v>
+        <v>-1.014107026076913</v>
       </c>
     </row>
     <row r="178">
@@ -2666,10 +2666,10 @@
         </is>
       </c>
       <c r="B178">
-        <v>-3.410954356931203</v>
+        <v>0.8821640216601436</v>
       </c>
       <c r="C178">
-        <v>0.8969317720810639</v>
+        <v>-1.785729063686531</v>
       </c>
     </row>
     <row r="179">
@@ -2679,10 +2679,10 @@
         </is>
       </c>
       <c r="B179">
-        <v>-0.02348756112567409</v>
+        <v>-1.636931070719601</v>
       </c>
       <c r="C179">
-        <v>0.5240611533536139</v>
+        <v>-0.9506365685681983</v>
       </c>
     </row>
     <row r="180">
@@ -2692,10 +2692,10 @@
         </is>
       </c>
       <c r="B180">
-        <v>-1.24139263268087</v>
+        <v>0.2912966540699464</v>
       </c>
       <c r="C180">
-        <v>-0.6446044751405335</v>
+        <v>0.4203051967090535</v>
       </c>
     </row>
     <row r="181">
@@ -2705,10 +2705,10 @@
         </is>
       </c>
       <c r="B181">
-        <v>0.8467309368114213</v>
+        <v>-0.03553753627801653</v>
       </c>
       <c r="C181">
-        <v>-0.1261816322505231</v>
+        <v>-0.2923536699350268</v>
       </c>
     </row>
     <row r="182">
@@ -2718,10 +2718,10 @@
         </is>
       </c>
       <c r="B182">
-        <v>-0.259668488961481</v>
+        <v>0.02038094278547038</v>
       </c>
       <c r="C182">
-        <v>-0.3013324558800182</v>
+        <v>-0.1878788349982448</v>
       </c>
     </row>
     <row r="183">
@@ -2731,10 +2731,10 @@
         </is>
       </c>
       <c r="B183">
-        <v>-0.08207458528972611</v>
+        <v>-0.07784359314686971</v>
       </c>
       <c r="C183">
-        <v>-0.8827347096312939</v>
+        <v>0.05329642792887684</v>
       </c>
     </row>
     <row r="184">
@@ -2744,10 +2744,10 @@
         </is>
       </c>
       <c r="B184">
-        <v>-0.2712980033102455</v>
+        <v>1.360834390100297</v>
       </c>
       <c r="C184">
-        <v>-1.095577530390049</v>
+        <v>0.3639028128640308</v>
       </c>
     </row>
     <row r="185">
@@ -2757,10 +2757,10 @@
         </is>
       </c>
       <c r="B185">
-        <v>-0.3275277638727201</v>
+        <v>0.9741957851865269</v>
       </c>
       <c r="C185">
-        <v>1.029053375567766</v>
+        <v>1.674001253029277</v>
       </c>
     </row>
     <row r="186">
@@ -2770,10 +2770,10 @@
         </is>
       </c>
       <c r="B186">
-        <v>-1.179157923001337</v>
+        <v>1.666158854860932</v>
       </c>
       <c r="C186">
-        <v>-1.225677156209755</v>
+        <v>1.098235869849617</v>
       </c>
     </row>
     <row r="187">
@@ -2783,10 +2783,10 @@
         </is>
       </c>
       <c r="B187">
-        <v>-1.878798312234184</v>
+        <v>-0.7371192088728351</v>
       </c>
       <c r="C187">
-        <v>-0.5240436799365812</v>
+        <v>-0.6520578151323229</v>
       </c>
     </row>
     <row r="188">
@@ -2796,10 +2796,10 @@
         </is>
       </c>
       <c r="B188">
-        <v>1.084350433714025</v>
+        <v>-1.451286123549472</v>
       </c>
       <c r="C188">
-        <v>0.521250782799233</v>
+        <v>-1.598450360603972</v>
       </c>
     </row>
     <row r="189">
@@ -2809,10 +2809,10 @@
         </is>
       </c>
       <c r="B189">
-        <v>-2.770369675177694</v>
+        <v>0.06045227492193395</v>
       </c>
       <c r="C189">
-        <v>1.309029471374539</v>
+        <v>0.4929995399130493</v>
       </c>
     </row>
     <row r="190">
@@ -2822,10 +2822,10 @@
         </is>
       </c>
       <c r="B190">
-        <v>1.307655013325102</v>
+        <v>0.4532015387436421</v>
       </c>
       <c r="C190">
-        <v>-1.728357514682243</v>
+        <v>1.112960861675109</v>
       </c>
     </row>
     <row r="191">
@@ -2835,10 +2835,10 @@
         </is>
       </c>
       <c r="B191">
-        <v>1.066051949313169</v>
+        <v>0.1946213986308526</v>
       </c>
       <c r="C191">
-        <v>0.6559620381415957</v>
+        <v>0.009148076482268702</v>
       </c>
     </row>
     <row r="192">
@@ -2848,10 +2848,10 @@
         </is>
       </c>
       <c r="B192">
-        <v>-0.3659212377647643</v>
+        <v>1.151421117213192</v>
       </c>
       <c r="C192">
-        <v>-1.201367044906059</v>
+        <v>-0.2440240031180634</v>
       </c>
     </row>
     <row r="193">
@@ -2861,10 +2861,10 @@
         </is>
       </c>
       <c r="B193">
-        <v>-1.332387519748834</v>
+        <v>-0.161337100839441</v>
       </c>
       <c r="C193">
-        <v>-1.245614785685313</v>
+        <v>0.4641007823355042</v>
       </c>
     </row>
     <row r="194">
@@ -2874,10 +2874,10 @@
         </is>
       </c>
       <c r="B194">
-        <v>-0.9328657133149559</v>
+        <v>0.2575389293003765</v>
       </c>
       <c r="C194">
-        <v>-0.6715379346495552</v>
+        <v>-0.4297796378173278</v>
       </c>
     </row>
     <row r="195">
@@ -2887,10 +2887,10 @@
         </is>
       </c>
       <c r="B195">
-        <v>0.1474430867249893</v>
+        <v>-0.5295206189779953</v>
       </c>
       <c r="C195">
-        <v>-1.328121516616656</v>
+        <v>-0.5972845986311556</v>
       </c>
     </row>
     <row r="196">
@@ -2900,10 +2900,10 @@
         </is>
       </c>
       <c r="B196">
-        <v>-0.9357003519507139</v>
+        <v>0.1062834650261779</v>
       </c>
       <c r="C196">
-        <v>-2.091892542852553</v>
+        <v>0.391959322687032</v>
       </c>
     </row>
     <row r="197">
@@ -2913,10 +2913,10 @@
         </is>
       </c>
       <c r="B197">
-        <v>-0.1389396007796827</v>
+        <v>-0.8027242560587412</v>
       </c>
       <c r="C197">
-        <v>-0.2640178461919624</v>
+        <v>-1.626822188321029</v>
       </c>
     </row>
     <row r="198">
@@ -2926,10 +2926,10 @@
         </is>
       </c>
       <c r="B198">
-        <v>0.05189871513987531</v>
+        <v>0.05933751905450986</v>
       </c>
       <c r="C198">
-        <v>-0.5214713128512323</v>
+        <v>0.3676450542184706</v>
       </c>
     </row>
     <row r="199">
@@ -2939,10 +2939,10 @@
         </is>
       </c>
       <c r="B199">
-        <v>2.811520424283163</v>
+        <v>-0.982987244006595</v>
       </c>
       <c r="C199">
-        <v>0.1755887453518151</v>
+        <v>0.2042174639256079</v>
       </c>
     </row>
     <row r="200">
@@ -2952,10 +2952,10 @@
         </is>
       </c>
       <c r="B200">
-        <v>0.7179925983644915</v>
+        <v>1.694285292065294</v>
       </c>
       <c r="C200">
-        <v>1.595405705151135</v>
+        <v>-0.2604090890017923</v>
       </c>
     </row>
     <row r="201">
@@ -2965,10 +2965,10 @@
         </is>
       </c>
       <c r="B201">
-        <v>-3.361918238351101</v>
+        <v>-0.2635385885430996</v>
       </c>
       <c r="C201">
-        <v>-0.9345394743728858</v>
+        <v>0.1866436612947442</v>
       </c>
     </row>
   </sheetData>
